--- a/output/laminas_comunales/comunal_o_ocup_a_2020_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,136 +375,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C2">
-        <v>36.6873280982182</v>
+        <v>55.6182860510595</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.1201882958461</v>
+        <v>55.5891106442577</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.0689047811048</v>
+        <v>55.3041820507252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C5">
-        <v>35.5762188676054</v>
+        <v>55.2648500924363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C6">
-        <v>35.5691914080072</v>
+        <v>54.1207375771134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C7">
-        <v>35.3007075471698</v>
+        <v>54.0590259678899</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C8">
-        <v>33.9912040917982</v>
+        <v>54.0106532978223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C9">
-        <v>32.1969123019681</v>
+        <v>53.8817467202987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="C10">
-        <v>32.0969828946538</v>
+        <v>53.3504054630815</v>
       </c>
     </row>
     <row r="11">
@@ -519,67 +519,1432 @@
         </is>
       </c>
       <c r="C11">
-        <v>30.3420038535645</v>
+        <v>51.0210264800339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C12">
-        <v>27.6960478743299</v>
+        <v>50.9323789790921</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C13">
-        <v>27.4763426058198</v>
+        <v>47.5803407106791</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C14">
-        <v>24.2747871265695</v>
+        <v>47.1426623022368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>46.2722852512156</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.6918780366502</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>45.4559278920593</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>45.1730666977914</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>45.0897647843615</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>45.0176516542451</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>44.8797038864898</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>44.1052547897289</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>44.0061715972362</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>43.7524015028913</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>43.691265624798</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>43.602718751167</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>43.5120829360081</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>43.3310243977526</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>43.3103787506148</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>42.9333465815835</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>42.8257712327958</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>4202</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Canela</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C32">
+        <v>42.4926453948857</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>41.5209933017481</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>40.8056274470768</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>40.7885162399947</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>40.61195488054</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>37.8564365696571</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>37.4450887366016</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>36.6873280982182</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>36.1201882958461</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.0689047811048</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>35.5844942459116</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>35.5762188676054</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>35.5691914080072</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>35.5388528202619</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>35.3007075471698</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>35.1378863594299</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>34.3670178799489</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>33.9912040917982</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>32.8073492340508</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>32.7358698042665</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>32.1969123019681</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>32.0969828946538</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>31.7442794058611</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>31.2473511337148</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>31.0430980637102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>31.0316435562043</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>30.7411787896708</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>30.4703183252079</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>30.3420038535645</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>29.7187668089684</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.2646402854776</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>29.2430507695842</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>29.0534951296368</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>29.0056709965177</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>28.7456267804982</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>27.8885247162176</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>27.8315065549108</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>27.8155339805825</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>27.7743723863621</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>27.7182520647456</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>27.6960478743299</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>27.6005047773571</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>27.5110945053604</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>27.4763426058198</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>27.0082582582583</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>26.6780908354256</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>26.5967820575329</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>25.3431708991078</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>24.8312393968514</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>24.7154225848695</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>24.2747871265695</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C83">
         <v>23.7691976460456</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>22.9671105730428</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>22.897036917389</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>22.378780199358</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>22.3631565506087</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>20.4508019072388</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>20.2954399486191</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>17.9982568274259</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>17.1920037192004</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>10.8429520811473</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>9.74698753966014</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>9.50564317577944</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>9.47861089939024</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>9.31335726010628</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>9.280923955179</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>8.91326500029971</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>8.760103751960431</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>8.40831981118159</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>7.85607906850799</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>7.80868457373394</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>7.00841009211053</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>7.00079554494829</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>6.66099371247577</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>5.54686918323282</v>
       </c>
     </row>
   </sheetData>
